--- a/00_Система/Инструменты/Python_Excel/ДСИ РСС фев 2026_v01.xlsx
+++ b/00_Система/Инструменты/Python_Excel/ДСИ РСС фев 2026_v01.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Oburec\AGrav\00_Система\Инструменты\Python_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Oburec\Antigravity\Projects\AGrav\00_Система\Инструменты\Python_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B26CB1-D969-4479-ADA7-B33FB5D41E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12345" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="380" yWindow="20" windowWidth="15250" windowHeight="10060" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="все" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,7 +26,18 @@
     <definedName name="Процент">#REF!</definedName>
     <definedName name="Чел_мес">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -564,7 +576,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1605,32 +1617,32 @@
   </cellXfs>
   <cellStyles count="27">
     <cellStyle name="Гиперссылка" xfId="16" builtinId="8"/>
-    <cellStyle name="Гиперссылка 2" xfId="26"/>
+    <cellStyle name="Гиперссылка 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="9"/>
-    <cellStyle name="Обычный 10 2" xfId="22"/>
-    <cellStyle name="Обычный 11" xfId="14"/>
-    <cellStyle name="Обычный 11 2" xfId="24"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="10"/>
-    <cellStyle name="Обычный 25" xfId="15"/>
-    <cellStyle name="Обычный 25 2" xfId="25"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный 3 2" xfId="12"/>
-    <cellStyle name="Обычный 4" xfId="3"/>
-    <cellStyle name="Обычный 4 2" xfId="17"/>
-    <cellStyle name="Обычный 5" xfId="4"/>
-    <cellStyle name="Обычный 5 2" xfId="11"/>
-    <cellStyle name="Обычный 5 2 2" xfId="23"/>
-    <cellStyle name="Обычный 5 3" xfId="18"/>
-    <cellStyle name="Обычный 6" xfId="5"/>
-    <cellStyle name="Обычный 6 2" xfId="19"/>
-    <cellStyle name="Обычный 7" xfId="6"/>
-    <cellStyle name="Обычный 7 2" xfId="13"/>
-    <cellStyle name="Обычный 8" xfId="7"/>
-    <cellStyle name="Обычный 8 2" xfId="20"/>
-    <cellStyle name="Обычный 9" xfId="8"/>
-    <cellStyle name="Обычный 9 2" xfId="21"/>
+    <cellStyle name="Обычный 10" xfId="9" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 10 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 11" xfId="14" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 11 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 25" xfId="15" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 25 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 4" xfId="3" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 5" xfId="4" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Обычный 5 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Обычный 5 2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Обычный 5 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Обычный 6" xfId="5" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Обычный 6 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Обычный 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Обычный 7 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Обычный 8" xfId="7" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Обычный 8 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Обычный 9" xfId="8" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Обычный 9 2" xfId="21" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1764,6 +1776,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1799,6 +1828,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1974,22 +2020,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="138" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="138" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="138" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="138" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="138" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="138" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="138" customWidth="1"/>
-    <col min="8" max="11" width="8.7109375" style="138" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" style="138" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="138" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" style="138" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="138" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="10.26953125" style="138" customWidth="1"/>
+    <col min="8" max="11" width="8.7265625" style="138" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2012,7 +2058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -2038,7 +2084,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -2064,7 +2110,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -2090,7 +2136,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -2113,7 +2159,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -2136,7 +2182,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -2159,7 +2205,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -2185,7 +2231,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -2208,7 +2254,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -2231,7 +2277,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
@@ -2254,7 +2300,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
@@ -2277,7 +2323,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>18</v>
       </c>
@@ -2300,7 +2346,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
@@ -2323,7 +2369,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
@@ -2346,7 +2392,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
@@ -2369,7 +2415,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
@@ -2392,7 +2438,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -2415,7 +2461,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
@@ -2438,7 +2484,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -2461,7 +2507,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -2484,7 +2530,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -2510,7 +2556,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>28</v>
       </c>
@@ -2533,7 +2579,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>29</v>
       </c>
@@ -2556,7 +2602,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>30</v>
       </c>
@@ -2579,7 +2625,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>31</v>
       </c>
@@ -2602,7 +2648,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>32</v>
       </c>
@@ -2625,7 +2671,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
@@ -2651,7 +2697,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
@@ -2674,7 +2720,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>35</v>
       </c>
@@ -2697,7 +2743,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>36</v>
       </c>
@@ -2717,7 +2763,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>37</v>
       </c>
@@ -2740,7 +2786,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>38</v>
       </c>
@@ -2769,7 +2815,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>39</v>
       </c>
@@ -2792,7 +2838,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>40</v>
       </c>
@@ -2821,7 +2867,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>41</v>
       </c>
@@ -2844,7 +2890,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>1</v>
       </c>
@@ -2873,69 +2919,69 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -2943,22 +2989,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
   <dimension ref="A2:M153"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="138" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="138" customWidth="1"/>
-    <col min="3" max="13" width="8.7109375" style="138" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" style="138" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="138" customWidth="1"/>
+    <col min="3" max="13" width="8.7265625" style="138" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>0</v>
       </c>
@@ -2997,7 +3043,7 @@
       </c>
       <c r="M4" s="33"/>
     </row>
-    <row r="5" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
@@ -3026,7 +3072,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -3053,7 +3099,7 @@
       <c r="L6" s="7"/>
       <c r="M6" s="140"/>
     </row>
-    <row r="7" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -3080,7 +3126,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="140"/>
     </row>
-    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -3107,7 +3153,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="140"/>
     </row>
-    <row r="9" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -3138,7 +3184,7 @@
       <c r="L9" s="7"/>
       <c r="M9" s="140"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
@@ -3174,7 +3220,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="140"/>
     </row>
-    <row r="11" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
@@ -3204,7 +3250,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="140"/>
     </row>
-    <row r="12" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -3231,7 +3277,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="140"/>
     </row>
-    <row r="13" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -3258,7 +3304,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="140"/>
     </row>
-    <row r="14" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3285,7 +3331,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="140"/>
     </row>
-    <row r="15" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3312,7 +3358,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="140"/>
     </row>
-    <row r="16" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
@@ -3339,7 +3385,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="140"/>
     </row>
-    <row r="17" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
@@ -3366,7 +3412,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="140"/>
     </row>
-    <row r="18" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -3393,7 +3439,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="140"/>
     </row>
-    <row r="19" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -3420,7 +3466,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="140"/>
     </row>
-    <row r="20" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
@@ -3447,7 +3493,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="140"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
@@ -3474,7 +3520,7 @@
       <c r="L21" s="7"/>
       <c r="M21" s="140"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
@@ -3501,7 +3547,7 @@
       <c r="L22" s="7"/>
       <c r="M22" s="140"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
@@ -3528,7 +3574,7 @@
       <c r="L23" s="7"/>
       <c r="M23" s="140"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
@@ -3555,7 +3601,7 @@
       <c r="L24" s="7"/>
       <c r="M24" s="140"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
@@ -3585,7 +3631,7 @@
       <c r="L25" s="7"/>
       <c r="M25" s="140"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -3612,7 +3658,7 @@
       <c r="L26" s="7"/>
       <c r="M26" s="140"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
@@ -3639,7 +3685,7 @@
       <c r="L27" s="7"/>
       <c r="M27" s="140"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
@@ -3666,7 +3712,7 @@
       <c r="L28" s="7"/>
       <c r="M28" s="140"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>31</v>
       </c>
@@ -3693,7 +3739,7 @@
       <c r="L29" s="7"/>
       <c r="M29" s="140"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
@@ -3735,7 +3781,7 @@
       </c>
       <c r="M30" s="140"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
@@ -3780,7 +3826,7 @@
       </c>
       <c r="M31" s="140"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
@@ -3807,7 +3853,7 @@
       <c r="L32" s="7"/>
       <c r="M32" s="140"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>35</v>
       </c>
@@ -3834,7 +3880,7 @@
       <c r="L33" s="27"/>
       <c r="M33" s="140"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>36</v>
       </c>
@@ -3854,7 +3900,7 @@
       <c r="L34" s="27"/>
       <c r="M34" s="140"/>
     </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>37</v>
       </c>
@@ -3874,7 +3920,7 @@
       <c r="L35" s="27"/>
       <c r="M35" s="140"/>
     </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>38</v>
       </c>
@@ -3897,7 +3943,7 @@
       <c r="L36" s="27"/>
       <c r="M36" s="140"/>
     </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>41</v>
       </c>
@@ -3924,7 +3970,7 @@
       <c r="L37" s="27"/>
       <c r="M37" s="140"/>
     </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17"/>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -3939,14 +3985,14 @@
       <c r="L38" s="19"/>
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
         <v>0</v>
       </c>
@@ -3985,7 +4031,7 @@
       </c>
       <c r="M42" s="33"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
         <v>7</v>
       </c>
@@ -4014,7 +4060,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>8</v>
       </c>
@@ -4041,7 +4087,7 @@
       <c r="L44" s="7"/>
       <c r="M44" s="140"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>9</v>
       </c>
@@ -4068,7 +4114,7 @@
       <c r="L45" s="7"/>
       <c r="M45" s="140"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>10</v>
       </c>
@@ -4095,7 +4141,7 @@
       <c r="L46" s="7"/>
       <c r="M46" s="140"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>11</v>
       </c>
@@ -4126,7 +4172,7 @@
       <c r="L47" s="7"/>
       <c r="M47" s="140"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>12</v>
       </c>
@@ -4162,7 +4208,7 @@
       <c r="L48" s="7"/>
       <c r="M48" s="140"/>
     </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>13</v>
       </c>
@@ -4192,7 +4238,7 @@
       <c r="L49" s="7"/>
       <c r="M49" s="140"/>
     </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>14</v>
       </c>
@@ -4219,7 +4265,7 @@
       <c r="L50" s="7"/>
       <c r="M50" s="140"/>
     </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>15</v>
       </c>
@@ -4246,7 +4292,7 @@
       <c r="L51" s="7"/>
       <c r="M51" s="140"/>
     </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>16</v>
       </c>
@@ -4273,7 +4319,7 @@
       <c r="L52" s="7"/>
       <c r="M52" s="140"/>
     </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>17</v>
       </c>
@@ -4300,7 +4346,7 @@
       <c r="L53" s="7"/>
       <c r="M53" s="140"/>
     </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>18</v>
       </c>
@@ -4327,7 +4373,7 @@
       <c r="L54" s="7"/>
       <c r="M54" s="140"/>
     </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>19</v>
       </c>
@@ -4354,7 +4400,7 @@
       <c r="L55" s="7"/>
       <c r="M55" s="140"/>
     </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>20</v>
       </c>
@@ -4381,7 +4427,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="140"/>
     </row>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>21</v>
       </c>
@@ -4408,7 +4454,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="140"/>
     </row>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>22</v>
       </c>
@@ -4435,7 +4481,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="140"/>
     </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>23</v>
       </c>
@@ -4462,7 +4508,7 @@
       <c r="L59" s="7"/>
       <c r="M59" s="140"/>
     </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>24</v>
       </c>
@@ -4489,7 +4535,7 @@
       <c r="L60" s="7"/>
       <c r="M60" s="140"/>
     </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>25</v>
       </c>
@@ -4516,7 +4562,7 @@
       <c r="L61" s="7"/>
       <c r="M61" s="140"/>
     </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
@@ -4543,7 +4589,7 @@
       <c r="L62" s="7"/>
       <c r="M62" s="140"/>
     </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>27</v>
       </c>
@@ -4573,7 +4619,7 @@
       <c r="L63" s="7"/>
       <c r="M63" s="140"/>
     </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>28</v>
       </c>
@@ -4600,7 +4646,7 @@
       <c r="L64" s="7"/>
       <c r="M64" s="140"/>
     </row>
-    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>29</v>
       </c>
@@ -4627,7 +4673,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="140"/>
     </row>
-    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>30</v>
       </c>
@@ -4654,7 +4700,7 @@
       <c r="L66" s="7"/>
       <c r="M66" s="140"/>
     </row>
-    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>31</v>
       </c>
@@ -4681,7 +4727,7 @@
       <c r="L67" s="7"/>
       <c r="M67" s="140"/>
     </row>
-    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>32</v>
       </c>
@@ -4723,7 +4769,7 @@
       </c>
       <c r="M68" s="140"/>
     </row>
-    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>33</v>
       </c>
@@ -4768,7 +4814,7 @@
       </c>
       <c r="M69" s="140"/>
     </row>
-    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>34</v>
       </c>
@@ -4795,7 +4841,7 @@
       <c r="L70" s="7"/>
       <c r="M70" s="140"/>
     </row>
-    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>35</v>
       </c>
@@ -4822,7 +4868,7 @@
       <c r="L71" s="27"/>
       <c r="M71" s="140"/>
     </row>
-    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>36</v>
       </c>
@@ -4842,7 +4888,7 @@
       <c r="L72" s="27"/>
       <c r="M72" s="140"/>
     </row>
-    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>37</v>
       </c>
@@ -4862,7 +4908,7 @@
       <c r="L73" s="27"/>
       <c r="M73" s="140"/>
     </row>
-    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>38</v>
       </c>
@@ -4885,7 +4931,7 @@
       <c r="L74" s="27"/>
       <c r="M74" s="140"/>
     </row>
-    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>41</v>
       </c>
@@ -4912,7 +4958,7 @@
       <c r="L75" s="27"/>
       <c r="M75" s="140"/>
     </row>
-    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="17"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
@@ -4927,17 +4973,17 @@
       <c r="L76" s="19"/>
       <c r="M76" s="18"/>
     </row>
-    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="141" t="s">
         <v>54</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="142"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="28" t="s">
         <v>0</v>
       </c>
@@ -4976,7 +5022,7 @@
       </c>
       <c r="M81" s="33"/>
     </row>
-    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
         <v>7</v>
       </c>
@@ -5003,7 +5049,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>8</v>
       </c>
@@ -5030,7 +5076,7 @@
       <c r="L83" s="7"/>
       <c r="M83" s="140"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>9</v>
       </c>
@@ -5057,7 +5103,7 @@
       <c r="L84" s="7"/>
       <c r="M84" s="140"/>
     </row>
-    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>10</v>
       </c>
@@ -5082,7 +5128,7 @@
       <c r="L85" s="7"/>
       <c r="M85" s="140"/>
     </row>
-    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>11</v>
       </c>
@@ -5113,7 +5159,7 @@
       <c r="L86" s="7"/>
       <c r="M86" s="140"/>
     </row>
-    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>12</v>
       </c>
@@ -5149,7 +5195,7 @@
       <c r="L87" s="7"/>
       <c r="M87" s="140"/>
     </row>
-    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>13</v>
       </c>
@@ -5179,7 +5225,7 @@
       <c r="L88" s="7"/>
       <c r="M88" s="140"/>
     </row>
-    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>14</v>
       </c>
@@ -5206,7 +5252,7 @@
       <c r="L89" s="7"/>
       <c r="M89" s="140"/>
     </row>
-    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>15</v>
       </c>
@@ -5231,7 +5277,7 @@
       <c r="L90" s="7"/>
       <c r="M90" s="140"/>
     </row>
-    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>16</v>
       </c>
@@ -5256,7 +5302,7 @@
       <c r="L91" s="7"/>
       <c r="M91" s="140"/>
     </row>
-    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>17</v>
       </c>
@@ -5283,7 +5329,7 @@
       <c r="L92" s="7"/>
       <c r="M92" s="140"/>
     </row>
-    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>18</v>
       </c>
@@ -5310,7 +5356,7 @@
       <c r="L93" s="7"/>
       <c r="M93" s="140"/>
     </row>
-    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>19</v>
       </c>
@@ -5337,7 +5383,7 @@
       <c r="L94" s="7"/>
       <c r="M94" s="140"/>
     </row>
-    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>20</v>
       </c>
@@ -5364,7 +5410,7 @@
       <c r="L95" s="7"/>
       <c r="M95" s="140"/>
     </row>
-    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>21</v>
       </c>
@@ -5391,7 +5437,7 @@
       <c r="L96" s="7"/>
       <c r="M96" s="140"/>
     </row>
-    <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>22</v>
       </c>
@@ -5418,7 +5464,7 @@
       <c r="L97" s="7"/>
       <c r="M97" s="140"/>
     </row>
-    <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>23</v>
       </c>
@@ -5445,7 +5491,7 @@
       <c r="L98" s="7"/>
       <c r="M98" s="140"/>
     </row>
-    <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>24</v>
       </c>
@@ -5472,7 +5518,7 @@
       <c r="L99" s="7"/>
       <c r="M99" s="140"/>
     </row>
-    <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>25</v>
       </c>
@@ -5499,7 +5545,7 @@
       <c r="L100" s="7"/>
       <c r="M100" s="140"/>
     </row>
-    <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>26</v>
       </c>
@@ -5526,7 +5572,7 @@
       <c r="L101" s="7"/>
       <c r="M101" s="140"/>
     </row>
-    <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>27</v>
       </c>
@@ -5556,7 +5602,7 @@
       <c r="L102" s="7"/>
       <c r="M102" s="140"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>28</v>
       </c>
@@ -5583,7 +5629,7 @@
       <c r="L103" s="7"/>
       <c r="M103" s="140"/>
     </row>
-    <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>29</v>
       </c>
@@ -5610,7 +5656,7 @@
       <c r="L104" s="7"/>
       <c r="M104" s="140"/>
     </row>
-    <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>30</v>
       </c>
@@ -5637,7 +5683,7 @@
       <c r="L105" s="7"/>
       <c r="M105" s="140"/>
     </row>
-    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>31</v>
       </c>
@@ -5664,7 +5710,7 @@
       <c r="L106" s="7"/>
       <c r="M106" s="140"/>
     </row>
-    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>32</v>
       </c>
@@ -5706,7 +5752,7 @@
       </c>
       <c r="M107" s="140"/>
     </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>33</v>
       </c>
@@ -5751,7 +5797,7 @@
       </c>
       <c r="M108" s="140"/>
     </row>
-    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>34</v>
       </c>
@@ -5778,7 +5824,7 @@
       <c r="L109" s="7"/>
       <c r="M109" s="140"/>
     </row>
-    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>35</v>
       </c>
@@ -5805,7 +5851,7 @@
       <c r="L110" s="27"/>
       <c r="M110" s="140"/>
     </row>
-    <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>36</v>
       </c>
@@ -5825,7 +5871,7 @@
       <c r="L111" s="27"/>
       <c r="M111" s="140"/>
     </row>
-    <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>37</v>
       </c>
@@ -5847,7 +5893,7 @@
       <c r="L112" s="27"/>
       <c r="M112" s="140"/>
     </row>
-    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>38</v>
       </c>
@@ -5870,7 +5916,7 @@
       <c r="L113" s="27"/>
       <c r="M113" s="140"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>41</v>
       </c>
@@ -5897,7 +5943,7 @@
       <c r="L114" s="27"/>
       <c r="M114" s="140"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="17"/>
       <c r="B115" s="19"/>
       <c r="C115" s="19"/>
@@ -5912,7 +5958,7 @@
       <c r="L115" s="19"/>
       <c r="M115" s="18"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="143" t="s">
         <v>55</v>
       </c>
@@ -5929,7 +5975,7 @@
       <c r="L116" s="144"/>
       <c r="M116" s="144"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="145"/>
       <c r="B117" s="145"/>
       <c r="C117" s="145"/>
@@ -5944,7 +5990,7 @@
       <c r="L117" s="145"/>
       <c r="M117" s="145"/>
     </row>
-    <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>0</v>
       </c>
@@ -5967,7 +6013,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>7</v>
       </c>
@@ -5988,7 +6034,7 @@
         <v>113430</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>8</v>
       </c>
@@ -6009,7 +6055,7 @@
         <v>58938</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>9</v>
       </c>
@@ -6030,7 +6076,7 @@
         <v>64100</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>10</v>
       </c>
@@ -6049,7 +6095,7 @@
         <v>21961</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>11</v>
       </c>
@@ -6068,7 +6114,7 @@
         <v>14380</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>12</v>
       </c>
@@ -6087,7 +6133,7 @@
         <v>27810.46999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>13</v>
       </c>
@@ -6108,7 +6154,7 @@
         <v>0.1199999999980719</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>14</v>
       </c>
@@ -6127,7 +6173,7 @@
         <v>16225.4</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>15</v>
       </c>
@@ -6146,7 +6192,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>16</v>
       </c>
@@ -6165,7 +6211,7 @@
         <v>5926.76</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>17</v>
       </c>
@@ -6184,7 +6230,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>18</v>
       </c>
@@ -6203,7 +6249,7 @@
         <v>23888.89</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>19</v>
       </c>
@@ -6222,7 +6268,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>20</v>
       </c>
@@ -6241,7 +6287,7 @@
         <v>21789.52</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>21</v>
       </c>
@@ -6260,7 +6306,7 @@
         <v>14153.58</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>22</v>
       </c>
@@ -6279,7 +6325,7 @@
         <v>11947.84</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>23</v>
       </c>
@@ -6298,7 +6344,7 @@
         <v>26788.6</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>24</v>
       </c>
@@ -6317,7 +6363,7 @@
         <v>17660.73</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>25</v>
       </c>
@@ -6336,7 +6382,7 @@
         <v>24792.89</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>26</v>
       </c>
@@ -6355,7 +6401,7 @@
         <v>22895</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>27</v>
       </c>
@@ -6376,7 +6422,7 @@
         <v>-759.55999999999767</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>28</v>
       </c>
@@ -6395,7 +6441,7 @@
         <v>5484</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>29</v>
       </c>
@@ -6414,7 +6460,7 @@
         <v>28354</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>30</v>
       </c>
@@ -6433,7 +6479,7 @@
         <v>29439.72</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>31</v>
       </c>
@@ -6452,7 +6498,7 @@
         <v>40115</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>32</v>
       </c>
@@ -6471,7 +6517,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>33</v>
       </c>
@@ -6492,7 +6538,7 @@
         <v>5660.6500000000005</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>34</v>
       </c>
@@ -6511,7 +6557,7 @@
         <v>20473.64</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>35</v>
       </c>
@@ -6530,7 +6576,7 @@
         <v>20421.72</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>36</v>
       </c>
@@ -6547,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
         <v>37</v>
       </c>
@@ -6564,7 +6610,7 @@
       <c r="F149" s="27"/>
       <c r="G149" s="5"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>38</v>
       </c>
@@ -6587,7 +6633,7 @@
         <v>45630</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
         <v>40</v>
       </c>
@@ -6610,7 +6656,7 @@
         <v>25500</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>41</v>
       </c>
@@ -6629,7 +6675,7 @@
         <v>15750</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="11" t="s">
         <v>1</v>
       </c>
@@ -6666,33 +6712,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Лист3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="138" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="138" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="138" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="138" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="138" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="138" customWidth="1"/>
-    <col min="7" max="7" width="50.28515625" style="138" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="138" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" style="138" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="138" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="138" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" style="138" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" style="138" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="138" customWidth="1"/>
+    <col min="7" max="7" width="50.26953125" style="138" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" style="138" customWidth="1"/>
     <col min="9" max="9" width="8" style="138" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="138" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="138" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="138" customWidth="1"/>
+    <col min="10" max="10" width="13.26953125" style="138" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" style="138" customWidth="1"/>
+    <col min="12" max="12" width="17.54296875" style="138" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
       <c r="G1" s="110" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="G2" s="62" t="s">
         <v>57</v>
       </c>
@@ -6701,7 +6747,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="47">
         <v>46054</v>
       </c>
@@ -6712,7 +6758,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="120" t="s">
         <v>60</v>
       </c>
@@ -6742,7 +6788,7 @@
       </c>
       <c r="L4" s="77"/>
     </row>
-    <row r="5" spans="2:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="121" t="s">
         <v>64</v>
       </c>
@@ -6772,7 +6818,7 @@
         <v>0.89399999999999991</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="121" t="s">
         <v>68</v>
       </c>
@@ -6811,7 +6857,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="122" t="s">
         <v>74</v>
       </c>
@@ -6844,7 +6890,7 @@
       </c>
       <c r="L7" s="117"/>
     </row>
-    <row r="8" spans="2:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="73"/>
       <c r="C8" s="82"/>
       <c r="D8" s="70"/>
@@ -6864,7 +6910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="43" t="s">
         <v>0</v>
       </c>
@@ -6893,7 +6939,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="44" t="s">
         <v>87</v>
       </c>
@@ -6913,18 +6959,16 @@
       <c r="G10" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="53">
-        <v>170</v>
-      </c>
+      <c r="H10" s="53"/>
       <c r="I10" s="41">
         <f t="shared" ref="I10:I24" si="1">F10-H10</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="J10" s="98">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="44" t="s">
         <v>90</v>
       </c>
@@ -6953,7 +6997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" ht="40.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="44" t="s">
         <v>93</v>
       </c>
@@ -6973,18 +7017,16 @@
       <c r="G12" s="135" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="53">
-        <v>245</v>
-      </c>
+      <c r="H12" s="53"/>
       <c r="I12" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="J12" s="98">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="45" t="s">
         <v>96</v>
       </c>
@@ -7004,18 +7046,16 @@
       <c r="G13" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="53">
-        <v>248.898</v>
-      </c>
+      <c r="H13" s="53"/>
       <c r="I13" s="41">
         <f t="shared" si="1"/>
-        <v>-63.897999999999996</v>
+        <v>185</v>
       </c>
       <c r="J13" s="98">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="67" t="s">
         <v>98</v>
       </c>
@@ -7035,18 +7075,16 @@
       <c r="G14" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="69">
-        <v>148.69499999999999</v>
-      </c>
+      <c r="H14" s="69"/>
       <c r="I14" s="41">
         <f t="shared" si="1"/>
-        <v>1.3050000000000068</v>
+        <v>150</v>
       </c>
       <c r="J14" s="84">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="67" t="s">
         <v>101</v>
       </c>
@@ -7066,18 +7104,16 @@
       <c r="G15" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="69">
-        <v>150</v>
-      </c>
+      <c r="H15" s="69"/>
       <c r="I15" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J15" s="98">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" ht="67.900000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="44" t="s">
         <v>104</v>
       </c>
@@ -7097,18 +7133,16 @@
       <c r="G16" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="53">
-        <v>383.04199999999997</v>
-      </c>
+      <c r="H16" s="53"/>
       <c r="I16" s="42">
         <f t="shared" si="1"/>
-        <v>-198.04199999999997</v>
+        <v>185</v>
       </c>
       <c r="J16" s="98">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:15" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" ht="42.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="44" t="s">
         <v>107</v>
       </c>
@@ -7128,12 +7162,10 @@
       <c r="G17" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="60">
-        <v>185</v>
-      </c>
+      <c r="H17" s="60"/>
       <c r="I17" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="J17" s="98">
         <v>1</v>
@@ -7142,7 +7174,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="44" t="s">
         <v>167</v>
       </c>
@@ -7178,7 +7210,7 @@
       </c>
       <c r="N18" s="137"/>
     </row>
-    <row r="19" spans="2:15" ht="89.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" ht="89.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="44" t="s">
         <v>113</v>
       </c>
@@ -7214,7 +7246,7 @@
       <c r="M19" s="65"/>
       <c r="N19" s="137"/>
     </row>
-    <row r="20" spans="2:15" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="44" t="s">
         <v>116</v>
       </c>
@@ -7234,19 +7266,17 @@
       <c r="G20" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="H20" s="61">
-        <v>220.8</v>
-      </c>
+      <c r="H20" s="61"/>
       <c r="I20" s="41">
         <f t="shared" si="1"/>
-        <v>-15.800000000000011</v>
+        <v>205</v>
       </c>
       <c r="J20" s="98">
         <v>1</v>
       </c>
       <c r="M20" s="65"/>
     </row>
-    <row r="21" spans="2:15" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="44" t="s">
         <v>118</v>
       </c>
@@ -7276,7 +7306,7 @@
       </c>
       <c r="M21" s="65"/>
     </row>
-    <row r="22" spans="2:15" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" ht="51.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="44" t="s">
         <v>120</v>
       </c>
@@ -7305,7 +7335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="44" t="s">
         <v>122</v>
       </c>
@@ -7334,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="44" t="s">
         <v>124</v>
       </c>
@@ -7354,18 +7384,16 @@
       <c r="G24" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H24" s="60">
-        <v>378</v>
-      </c>
+      <c r="H24" s="60"/>
       <c r="I24" s="41">
         <f t="shared" si="1"/>
-        <v>-203</v>
+        <v>175</v>
       </c>
       <c r="J24" s="84">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="55"/>
       <c r="C25" s="56"/>
       <c r="D25" s="57"/>
@@ -7375,7 +7403,7 @@
       <c r="H25" s="50"/>
       <c r="I25" s="50"/>
     </row>
-    <row r="26" spans="2:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E26" s="123" t="s">
         <v>126</v>
       </c>
@@ -7388,7 +7416,7 @@
       <c r="I26" s="50"/>
       <c r="J26" s="65"/>
     </row>
-    <row r="27" spans="2:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="73" t="s">
         <v>127</v>
       </c>
@@ -7413,7 +7441,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="82">
         <f>100*12*(F27-F26)/(F29*10^3)</f>
         <v>8.8974457088797099</v>
@@ -7440,7 +7468,7 @@
         <v>0.22286568437179463</v>
       </c>
     </row>
-    <row r="29" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E29" s="126" t="s">
         <v>135</v>
       </c>
@@ -7453,7 +7481,7 @@
       </c>
       <c r="H29" s="130"/>
     </row>
-    <row r="30" spans="2:15" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E30" s="127" t="s">
         <v>137</v>
       </c>
@@ -7489,7 +7517,7 @@
       </c>
       <c r="O30" s="87"/>
     </row>
-    <row r="31" spans="2:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E31" s="127" t="s">
         <v>140</v>
       </c>
@@ -7511,7 +7539,7 @@
       </c>
       <c r="M31" s="77"/>
     </row>
-    <row r="34" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E34" s="70" t="s">
         <v>144</v>
       </c>
@@ -7522,7 +7550,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E35" s="70" t="s">
         <v>146</v>
       </c>
@@ -7533,7 +7561,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E36" s="70" t="s">
         <v>148</v>
       </c>
@@ -7544,7 +7572,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E37" s="70" t="s">
         <v>150</v>
       </c>
@@ -7555,7 +7583,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="38" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:7" x14ac:dyDescent="0.35">
       <c r="E38" s="70" t="s">
         <v>150</v>
       </c>
@@ -7598,9 +7626,9 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="G1" r:id="rId1" location="gid=188003400" display="https://docs.google.com/spreadsheets/d/1mUoVyqMvLxNkew3nU1ZeJ1OjpYy3j-FOVDpqwsZ9BPU/edit?gid=188003400#gid=188003400"/>
-    <hyperlink ref="G2" r:id="rId2" display="&quot;\\Fserv\e\MERA\WORKS\ДСИ\РСС\3. Документы\командировки\ДСИ РСС командировки 2023_v01.xlsx&quot; "/>
-    <hyperlink ref="G3" r:id="rId3" location="gid=445756468"/>
+    <hyperlink ref="G1" r:id="rId1" location="gid=188003400" display="https://docs.google.com/spreadsheets/d/1mUoVyqMvLxNkew3nU1ZeJ1OjpYy3j-FOVDpqwsZ9BPU/edit?gid=188003400#gid=188003400" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G2" r:id="rId2" display="&quot;\\Fserv\e\MERA\WORKS\ДСИ\РСС\3. Документы\командировки\ДСИ РСС командировки 2023_v01.xlsx&quot; " xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G3" r:id="rId3" location="gid=445756468" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape"/>
@@ -7608,17 +7636,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" style="138" customWidth="1"/>
-    <col min="3" max="3" width="55.42578125" style="138" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="138" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="138" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="138" customWidth="1"/>
+    <col min="3" max="3" width="55.453125" style="138" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" style="138" customWidth="1"/>
+    <col min="5" max="5" width="44.453125" style="138" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" s="70" t="s">
         <v>153</v>
       </c>
@@ -7632,7 +7660,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="70" t="s">
         <v>156</v>
       </c>
@@ -7646,7 +7674,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="70" t="s">
         <v>62</v>
       </c>
@@ -7654,7 +7682,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="70" t="s">
         <v>140</v>
       </c>
@@ -7662,7 +7690,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="70" t="s">
         <v>161</v>
       </c>
@@ -7670,7 +7698,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
         <v>163</v>
       </c>
@@ -7678,7 +7706,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" ht="103.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="73" t="s">
         <v>165</v>
       </c>
